--- a/outputs/15387.xlsx
+++ b/outputs/15387.xlsx
@@ -143,12 +143,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -347,179 +351,180 @@
   <dimension ref="A1:H14"/>
   <sheetFormatPr defaultColWidth="8.8359375" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="n">
+      <c r="B1" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="C1" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="D1" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="E1" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="F1" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>50</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="F4" s="0" t="n">
+      <c r="F4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="1" t="n">
         <f aca="false">SUM(B4:F4)</f>
         <v>150</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="0" t="n">
+      <c r="F5" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="H5" s="1" t="n">
         <f aca="false">SUM(B5:F5)</f>
         <v>26</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <f aca="false">B4*B5</f>
         <v>200</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <f aca="false">C4*C5</f>
         <v>100</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <f aca="false">D4*D5</f>
         <v>120</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1" t="n">
         <f aca="false">E4*E5</f>
         <v>240</v>
       </c>
-      <c r="F6" s="0" t="n">
+      <c r="F6" s="1" t="n">
         <f aca="false">F4*F5</f>
         <v>70</v>
       </c>
-      <c r="H6" s="0" t="n">
+      <c r="H6" s="1" t="n">
         <f aca="false">SUM(B6:F6)</f>
         <v>730</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <f aca="false">B6*B1</f>
         <v>0</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <f aca="false">C6*C1</f>
         <v>100</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <f aca="false">D6*D1</f>
         <v>120</v>
       </c>
-      <c r="E9" s="0" t="n">
+      <c r="E9" s="1" t="n">
         <f aca="false">E6*E1</f>
         <v>0</v>
       </c>
-      <c r="F9" s="0" t="n">
+      <c r="F9" s="1" t="n">
         <f aca="false">F6*F1</f>
         <v>70</v>
       </c>
-      <c r="H9" s="0" t="n">
+      <c r="H9" s="1" t="n">
         <f aca="false">SUM(B9:F9)</f>
         <v>290</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="str">
-        <f aca="false" t="array" ref="A13:A14">IFERROR(INDEX($B$3:$F$3,SMALL(IF($B$1:$F$1=0,COLUMN($B$1:$F$1)-COLUMN($B$1)+1),ROW()-12)),"")</f>
+      <c r="A13" s="1" t="str">
+        <f aca="false">INDEX($B$3:$F$3,MATCH(0,$B$1:$F$1,0))</f>
         <v>A</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="str">
+      <c r="A14" s="1" t="str">
+        <f aca="true">INDEX($B$3:$F$3,MATCH(0,$B$1:$F$1,0)+MATCH(0,OFFSET($B$1:$F$1,0,MATCH(0,$B$1:$F$1,0)),0))</f>
         <v>D</v>
       </c>
     </row>

--- a/outputs/15387.xlsx
+++ b/outputs/15387.xlsx
@@ -517,15 +517,15 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="str">
-        <f aca="false">INDEX($B$3:$F$3,MATCH(0,$B$1:$F$1,0))</f>
-        <v>A</v>
+      <c r="A13" s="1" t="n">
+        <f aca="false">INDEX($C$4:$E$4,MATCH(1,$B$1:$D$1*($C$4:$E$4&gt;0),0))</f>
+        <v>30</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="str">
-        <f aca="true">INDEX($B$3:$F$3,MATCH(0,$B$1:$F$1,0)+MATCH(0,OFFSET($B$1:$F$1,0,MATCH(0,$B$1:$F$1,0)),0))</f>
-        <v>D</v>
+      <c r="A14" s="1" t="n">
+        <f aca="false">INDEX($C$4:$E$4,MATCH(1,$B$1:$D$1*($C$4:$E$4&gt;0),0)+1)</f>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
